--- a/InputData/elec/TACFMfPBTY/Time Adjusted Capacity Factor Multiplier for Plants Built This Year.xlsx
+++ b/InputData/elec/TACFMfPBTY/Time Adjusted Capacity Factor Multiplier for Plants Built This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\TACFMfPBTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6D6DBE-C177-4B4E-AB68-7539FB6A2B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F4036F-DB6E-4E4C-B822-CCA3A720CD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="6690" windowWidth="24240" windowHeight="13020" xr2:uid="{EBD0EF52-E4BC-4E99-950E-1B8A93112F65}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EBD0EF52-E4BC-4E99-950E-1B8A93112F65}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -272,7 +272,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -640,17 +639,17 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1240,7 +1239,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B24">
@@ -1248,7 +1247,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B25">
